--- a/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
+++ b/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
+++ b/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
+++ b/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
+++ b/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
+++ b/docs/StructureDefinition-EnvironmentalMonitoringLogicalModel.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="218">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/EnvironmentalMonitoringLogicalModel</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/EnvironmentalMonitoringLogicalModel</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -920,27 +923,29 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -948,26 +953,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1019,112 +1024,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -1140,10 +1145,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1155,7 +1160,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1212,13 +1217,13 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
@@ -1229,10 +1234,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1240,10 +1245,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1255,13 +1260,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1312,27 +1317,27 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1340,10 +1345,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1355,13 +1360,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1412,13 +1417,13 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
@@ -1429,21 +1434,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1455,16 +1460,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1502,74 +1507,74 @@
         <v>20</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>20</v>
@@ -1618,27 +1623,27 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1646,10 +1651,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1661,13 +1666,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1718,13 +1723,13 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1746,10 +1751,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1761,13 +1766,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1818,13 +1823,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1835,10 +1840,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1846,10 +1851,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1861,13 +1866,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1918,13 +1923,13 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
@@ -1935,10 +1940,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1946,10 +1951,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1961,13 +1966,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2018,13 +2023,13 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2046,10 +2051,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2061,13 +2066,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2118,13 +2123,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -2135,10 +2140,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2146,10 +2151,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2161,13 +2166,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2218,13 +2223,13 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
@@ -2235,10 +2240,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2246,10 +2251,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2261,13 +2266,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2318,27 +2323,27 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2346,10 +2351,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2361,13 +2366,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2418,13 +2423,13 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
@@ -2435,21 +2440,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2461,16 +2466,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2508,74 +2513,74 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -2624,27 +2629,27 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2652,10 +2657,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2667,13 +2672,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2724,13 +2729,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -2741,10 +2746,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2752,10 +2757,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2767,13 +2772,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2824,13 +2829,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2841,10 +2846,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2852,10 +2857,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2867,13 +2872,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2924,13 +2929,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -2941,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2952,10 +2957,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2967,13 +2972,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3024,13 +3029,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3052,10 +3057,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3067,13 +3072,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3124,13 +3129,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -3141,10 +3146,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3152,10 +3157,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3167,13 +3172,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3224,13 +3229,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -3241,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3252,10 +3257,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3267,13 +3272,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3324,13 +3329,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -3341,10 +3346,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3352,10 +3357,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3367,13 +3372,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3424,13 +3429,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -3441,10 +3446,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3452,10 +3457,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3467,13 +3472,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3524,27 +3529,27 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3552,10 +3557,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3567,13 +3572,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3624,13 +3629,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -3641,21 +3646,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -3667,16 +3672,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3714,74 +3719,74 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -3830,27 +3835,27 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3858,10 +3863,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -3873,13 +3878,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3930,13 +3935,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -3947,10 +3952,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3958,10 +3963,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -3973,13 +3978,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4030,13 +4035,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -4047,10 +4052,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4058,10 +4063,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4073,13 +4078,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4130,13 +4135,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -4147,10 +4152,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4158,10 +4163,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4173,13 +4178,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4230,13 +4235,13 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
@@ -4247,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4258,10 +4263,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -4273,13 +4278,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4330,13 +4335,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -4347,10 +4352,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4358,10 +4363,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -4373,13 +4378,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4430,13 +4435,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -4447,10 +4452,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4458,10 +4463,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -4473,13 +4478,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4530,13 +4535,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -4547,10 +4552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4558,10 +4563,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -4573,13 +4578,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4630,13 +4635,13 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -4647,10 +4652,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4658,10 +4663,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -4673,13 +4678,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4730,13 +4735,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -4747,10 +4752,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4758,10 +4763,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -4773,13 +4778,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4830,13 +4835,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -4847,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4858,10 +4863,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -4873,13 +4878,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4930,13 +4935,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -4947,10 +4952,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4958,10 +4963,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -4973,13 +4978,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5030,13 +5035,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -5047,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5058,10 +5063,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5073,13 +5078,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5130,27 +5135,27 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5158,10 +5163,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -5173,13 +5178,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5230,13 +5235,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -5247,21 +5252,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -5273,16 +5278,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5320,74 +5325,74 @@
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -5436,27 +5441,27 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5464,10 +5469,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -5479,13 +5484,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5536,13 +5541,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -5553,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5564,10 +5569,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -5579,13 +5584,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5636,13 +5641,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -5653,10 +5658,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5664,10 +5669,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -5679,13 +5684,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5736,13 +5741,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -5753,10 +5758,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5764,10 +5769,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -5779,13 +5784,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5836,13 +5841,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -5853,10 +5858,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5864,10 +5869,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -5879,13 +5884,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -5936,13 +5941,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -5953,10 +5958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -5964,10 +5969,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -5979,13 +5984,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6036,27 +6041,27 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6064,10 +6069,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -6079,13 +6084,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6136,13 +6141,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -6153,21 +6158,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -6179,16 +6184,16 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6226,74 +6231,74 @@
         <v>20</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -6342,27 +6347,27 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6370,10 +6375,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -6385,13 +6390,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6442,13 +6447,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -6459,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6470,10 +6475,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -6485,13 +6490,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6542,13 +6547,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -6559,10 +6564,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6570,10 +6575,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -6585,13 +6590,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6642,13 +6647,13 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
@@ -6659,10 +6664,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6670,10 +6675,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -6685,13 +6690,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6742,13 +6747,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -6759,10 +6764,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6770,10 +6775,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -6785,13 +6790,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -6842,13 +6847,13 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
@@ -6859,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -6870,10 +6875,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -6885,13 +6890,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -6942,27 +6947,27 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -6970,10 +6975,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -6985,13 +6990,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7042,13 +7047,13 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
@@ -7059,21 +7064,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -7085,16 +7090,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7132,74 +7137,74 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -7248,27 +7253,27 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7276,10 +7281,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -7291,13 +7296,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7348,13 +7353,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -7365,10 +7370,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7376,10 +7381,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -7391,13 +7396,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7448,13 +7453,13 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
@@ -7465,10 +7470,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7476,10 +7481,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -7491,13 +7496,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7548,13 +7553,13 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
@@ -7565,10 +7570,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7576,10 +7581,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -7591,13 +7596,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7648,13 +7653,13 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -7665,10 +7670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7676,10 +7681,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -7691,13 +7696,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -7748,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
@@ -7765,10 +7770,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -7776,10 +7781,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -7791,13 +7796,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -7848,13 +7853,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -7865,10 +7870,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -7876,10 +7881,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -7891,13 +7896,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -7948,13 +7953,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
